--- a/src/assets/overtime_template.xlsx
+++ b/src/assets/overtime_template.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://bbcgroup365.sharepoint.com/sites/CEP-O-OgolnePL-HR/Shared Documents/HR/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="30" documentId="13_ncr:1_{4853A9B9-1D28-4D7F-B792-A1A904D0EE10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{65D3C8FA-6DC0-414B-A25A-7F9F72589715}"/>
+  <xr:revisionPtr revIDLastSave="21" documentId="8_{5A03FAE7-36E5-4FC9-97F0-DBC5D6CC8125}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{23A7BA02-86A3-4EA1-80D5-004DBCD59EC5}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{5C54F8F0-E29B-4B1D-B5B0-84E7A0453ECD}"/>
   </bookViews>
   <sheets>
     <sheet name="Arkusz1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -68,6 +68,10 @@
   </si>
   <si>
     <t>LP</t>
+  </si>
+  <si>
+    <t>żółte wiersze do uzupełnienia obowiązkowo
+pozostałe opcjonalnie</t>
   </si>
   <si>
     <t>RAZEM</t>
@@ -99,12 +103,6 @@
     </r>
   </si>
   <si>
-    <t>WD</t>
-  </si>
-  <si>
-    <t>WN</t>
-  </si>
-  <si>
     <r>
       <t xml:space="preserve">Godziny </t>
     </r>
@@ -132,6 +130,23 @@
   </si>
   <si>
     <r>
+      <t xml:space="preserve">Liczba przepracowanych godzin
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial Narrow"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>-  czas pracy</t>
+    </r>
+  </si>
+  <si>
+    <r>
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
@@ -156,223 +171,6 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">Dni wolne od pracy </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial Narrow"/>
-        <family val="2"/>
-        <charset val="238"/>
-      </rPr>
-      <t>oraz tytuł ich udzielenia</t>
-    </r>
-  </si>
-  <si>
-    <t>Dyżury</t>
-  </si>
-  <si>
-    <t>od godziny</t>
-  </si>
-  <si>
-    <t>do godziny</t>
-  </si>
-  <si>
-    <t>liczba godzin</t>
-  </si>
-  <si>
-    <t>miejsce pełnienia dyżuru</t>
-  </si>
-  <si>
-    <t>Zwolnienia od pracy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">rodzaj </t>
-  </si>
-  <si>
-    <t>wymiar</t>
-  </si>
-  <si>
-    <t>Nieobecności usprawiedliwione</t>
-  </si>
-  <si>
-    <r>
-      <t>Nieobecności nieusprawiedliwione -</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial Narrow"/>
-        <family val="2"/>
-        <charset val="238"/>
-      </rPr>
-      <t>wymiar</t>
-    </r>
-  </si>
-  <si>
-    <t>Uwagi:</t>
-  </si>
-  <si>
-    <t>Legenda:</t>
-  </si>
-  <si>
-    <t>wolna niedziela</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> wolne z tytułu pięciodniowego tygodnia pracy</t>
-  </si>
-  <si>
-    <t>WŚ</t>
-  </si>
-  <si>
-    <t>wolne święto</t>
-  </si>
-  <si>
-    <t>zwolnienie lekarskie
-L-4</t>
-  </si>
-  <si>
-    <t>ZWO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">zwolnienie lekarskie-opieka </t>
-  </si>
-  <si>
-    <t>UW</t>
-  </si>
-  <si>
-    <t>urlop wypoczynkowy</t>
-  </si>
-  <si>
-    <t>UWŻ</t>
-  </si>
-  <si>
-    <t>urlop wypoczynkowy na żądanie</t>
-  </si>
-  <si>
-    <t>UOP</t>
-  </si>
-  <si>
-    <t>urlop -opieka nad dzieckiem do lat 14</t>
-  </si>
-  <si>
-    <t>UOK</t>
-  </si>
-  <si>
-    <t>urlop okolicznościowy</t>
-  </si>
-  <si>
-    <t>UNP</t>
-  </si>
-  <si>
-    <t>urlop z tyt. niepełnosprawności</t>
-  </si>
-  <si>
-    <t>UB</t>
-  </si>
-  <si>
-    <t>urlop bezpłatny</t>
-  </si>
-  <si>
-    <t>urlop macierzyński</t>
-  </si>
-  <si>
-    <t>URODZ</t>
-  </si>
-  <si>
-    <t>urlop rodzicielski</t>
-  </si>
-  <si>
-    <t>Uwych</t>
-  </si>
-  <si>
-    <t>urlop wychowawczy</t>
-  </si>
-  <si>
-    <t>UO</t>
-  </si>
-  <si>
-    <t>urlop ojcowski</t>
-  </si>
-  <si>
-    <t>USZK</t>
-  </si>
-  <si>
-    <t>urlop szkoleniowy</t>
-  </si>
-  <si>
-    <t>SZKOL</t>
-  </si>
-  <si>
-    <t>szkolenie</t>
-  </si>
-  <si>
-    <t>ŚWREH</t>
-  </si>
-  <si>
-    <t>świadczenie rehabilitacyjne</t>
-  </si>
-  <si>
-    <t>DEL</t>
-  </si>
-  <si>
-    <t>delegacja</t>
-  </si>
-  <si>
-    <t>WP</t>
-  </si>
-  <si>
-    <t>wyjścia prywatne
-(niezaliczony czas)</t>
-  </si>
-  <si>
-    <t>NU</t>
-  </si>
-  <si>
-    <t>nieobeność usprawiedliwiona-inna niż wymienione</t>
-  </si>
-  <si>
-    <t>DWNg</t>
-  </si>
-  <si>
-    <t>dzień wolny 
-za nadgodziny</t>
-  </si>
-  <si>
-    <t>DWNd</t>
-  </si>
-  <si>
-    <t>dzień wolny za pracę 
-w niedzielę</t>
-  </si>
-  <si>
-    <t>DWSo</t>
-  </si>
-  <si>
-    <t>dzień wolny 
-za pracę w sobotę</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Liczba przepracowanych godzin
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial Narrow"/>
-        <family val="2"/>
-        <charset val="238"/>
-      </rPr>
-      <t>-  czas pracy</t>
-    </r>
-  </si>
-  <si>
-    <r>
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
@@ -395,23 +193,225 @@
     </r>
   </si>
   <si>
+    <r>
+      <t xml:space="preserve">Dni wolne od pracy </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial Narrow"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>oraz tytuł ich udzielenia</t>
+    </r>
+  </si>
+  <si>
+    <t>Dyżury</t>
+  </si>
+  <si>
+    <t>od godziny</t>
+  </si>
+  <si>
+    <t>do godziny</t>
+  </si>
+  <si>
+    <t>liczba godzin</t>
+  </si>
+  <si>
+    <t>miejsce pełnienia dyżuru</t>
+  </si>
+  <si>
+    <t>Zwolnienia od pracy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rodzaj </t>
+  </si>
+  <si>
+    <t>wymiar</t>
+  </si>
+  <si>
+    <t>Nieobecności usprawiedliwione</t>
+  </si>
+  <si>
+    <r>
+      <t>Nieobecności nieusprawiedliwione -</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial Narrow"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>wymiar</t>
+    </r>
+  </si>
+  <si>
+    <t>Uwagi:</t>
+  </si>
+  <si>
+    <t>Legenda:</t>
+  </si>
+  <si>
+    <t>WN</t>
+  </si>
+  <si>
+    <t>wolna niedziela</t>
+  </si>
+  <si>
+    <t>WD</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> wolne z tytułu pięciodniowego tygodnia pracy</t>
+  </si>
+  <si>
+    <t>WŚ</t>
+  </si>
+  <si>
+    <t>wolne święto</t>
+  </si>
+  <si>
+    <t>SOBOTA</t>
+  </si>
+  <si>
     <t>CH</t>
   </si>
   <si>
+    <t>zwolnienie lekarskie
+L-4</t>
+  </si>
+  <si>
+    <t>ZWO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">zwolnienie lekarskie-opieka </t>
+  </si>
+  <si>
+    <t>UW</t>
+  </si>
+  <si>
+    <t>urlop wypoczynkowy</t>
+  </si>
+  <si>
+    <t>UWŻ</t>
+  </si>
+  <si>
+    <t>urlop wypoczynkowy na żądanie</t>
+  </si>
+  <si>
+    <t>UOP</t>
+  </si>
+  <si>
+    <t>urlop -opieka nad dzieckiem do lat 14</t>
+  </si>
+  <si>
+    <t>UOK</t>
+  </si>
+  <si>
+    <t>urlop okolicznościowy</t>
+  </si>
+  <si>
+    <t>UNP</t>
+  </si>
+  <si>
+    <t>urlop z tyt. niepełnosprawności</t>
+  </si>
+  <si>
+    <t>UB</t>
+  </si>
+  <si>
+    <t>urlop bezpłatny</t>
+  </si>
+  <si>
+    <t>NIEDZIELA</t>
+  </si>
+  <si>
     <t>UM</t>
   </si>
   <si>
-    <t>żółte wiersze do uzupełnienia obowiązkowo
-pozostałe opcjonalnie</t>
-  </si>
-  <si>
-    <t>SOBOTA</t>
-  </si>
-  <si>
-    <t>NIEDZIELA</t>
+    <t>urlop macierzyński</t>
+  </si>
+  <si>
+    <t>URODZ</t>
+  </si>
+  <si>
+    <t>urlop rodzicielski</t>
+  </si>
+  <si>
+    <t>Uwych</t>
+  </si>
+  <si>
+    <t>urlop wychowawczy</t>
+  </si>
+  <si>
+    <t>UO</t>
+  </si>
+  <si>
+    <t>urlop ojcowski</t>
+  </si>
+  <si>
+    <t>USZK</t>
+  </si>
+  <si>
+    <t>urlop szkoleniowy</t>
+  </si>
+  <si>
+    <t>SZKOL</t>
+  </si>
+  <si>
+    <t>szkolenie</t>
+  </si>
+  <si>
+    <t>ŚWREH</t>
+  </si>
+  <si>
+    <t>świadczenie rehabilitacyjne</t>
+  </si>
+  <si>
+    <t>DEL</t>
+  </si>
+  <si>
+    <t>delegacja</t>
   </si>
   <si>
     <t>ŚWIĘTO</t>
+  </si>
+  <si>
+    <t>WP</t>
+  </si>
+  <si>
+    <t>wyjścia prywatne
+(niezaliczony czas)</t>
+  </si>
+  <si>
+    <t>NU</t>
+  </si>
+  <si>
+    <t>nieobeność usprawiedliwiona-inna niż wymienione</t>
+  </si>
+  <si>
+    <t>DWNg</t>
+  </si>
+  <si>
+    <t>dzień wolny 
+za nadgodziny</t>
+  </si>
+  <si>
+    <t>DWNd</t>
+  </si>
+  <si>
+    <t>dzień wolny za pracę 
+w niedzielę</t>
+  </si>
+  <si>
+    <t>DWSo</t>
+  </si>
+  <si>
+    <t>dzień wolny 
+za pracę w sobotę</t>
   </si>
 </sst>
 </file>
@@ -936,6 +936,15 @@
     <xf numFmtId="0" fontId="10" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="24" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1097,21 +1106,60 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normalny" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="134">
+  <dxfs count="270">
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FFC00000"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFCDCD"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FFC00000"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFCDCD"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FFC00000"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFCDCD"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FFC00000"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFCDCD"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -1150,6 +1198,18 @@
     </dxf>
     <dxf>
       <font>
+        <b val="0"/>
+        <i val="0"/>
+        <color rgb="FF005C00"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FFC00000"/>
       </font>
       <fill>
@@ -1160,6 +1220,56 @@
     </dxf>
     <dxf>
       <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFE1E1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC00000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFCDCD"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.14996795556505021"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <b val="0"/>
         <i val="0"/>
         <color rgb="FF005C00"/>
@@ -1172,6 +1282,71 @@
     </dxf>
     <dxf>
       <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFCDEBFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFF5F9FD"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <color rgb="FF005C00"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <color rgb="FF005C00"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FFC00000"/>
       </font>
       <fill>
@@ -1182,6 +1357,16 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FFC00000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color auto="1"/>
       </font>
       <fill>
@@ -1206,6 +1391,146 @@
       </font>
       <fill>
         <patternFill>
+          <bgColor theme="0" tint="-0.14996795556505021"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FF006600"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FF006600"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF0000FF"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF0000FF"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF0000FF"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC00000"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="3" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC00000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF0000FF"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF0000FF"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF0000FF"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.14996795556505021"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
           <bgColor theme="9" tint="0.79998168889431442"/>
         </patternFill>
       </fill>
@@ -1231,6 +1556,203 @@
       </fill>
     </dxf>
     <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFCDEBFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFF5F9FD"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <color rgb="FF005C00"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <color rgb="FF005C00"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <color rgb="FF005C00"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC00000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC00000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFE1E1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFCDCD"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF008000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF008000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF0000FF"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFF5F9FD"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFCDEBFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFCDEBFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFF5F9FD"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <color rgb="FF005C00"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC00000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFCDCD"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
       <font>
         <color auto="1"/>
       </font>
@@ -1265,6 +1787,158 @@
       </fill>
     </dxf>
     <dxf>
+      <font>
+        <color rgb="FFC00000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFE1E1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFE1E1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFCDCD"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.14996795556505021"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC00000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC00000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <color rgb="FF005C00"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <color rgb="FF005C00"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <color rgb="FF005C00"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFF5F9FD"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
       <fill>
         <patternFill>
           <bgColor rgb="FFCDEBFF"/>
@@ -1273,6 +1947,523 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC00000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="3" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC00000"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF0000FF"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF0000FF"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF0000FF"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF0000FF"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF0000FF"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF0000FF"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FF006600"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FF006600"/>
+      </font>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFE5E5"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFD3E6F5"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <color rgb="FF006600"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <color rgb="FF006600"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <color rgb="FFC00000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <color rgb="FFC00000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFD9D9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFE7E7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC00000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <color rgb="FFC00000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <color rgb="FF005000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <color rgb="FF005000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC00000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC00000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFE1E1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFCDCD"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.14996795556505021"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <color rgb="FF005C00"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <color rgb="FF005C00"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <color rgb="FF005C00"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <color rgb="FF005C00"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <color rgb="FF005C00"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <color rgb="FF005C00"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC00000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFE1E1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC00000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFCDCD"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.14996795556505021"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <color rgb="FF005C00"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFCDEBFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <b val="0"/>
         <i val="0"/>
         <color auto="1"/>
@@ -1309,6 +2500,18 @@
     </dxf>
     <dxf>
       <font>
+        <b val="0"/>
+        <i val="0"/>
+        <color rgb="FF005C00"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FFC00000"/>
       </font>
       <fill>
@@ -1349,6 +2552,16 @@
     </dxf>
     <dxf>
       <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.14996795556505021"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <b/>
         <i val="0"/>
         <color rgb="FF006600"/>
@@ -1473,6 +2686,16 @@
       </font>
       <fill>
         <patternFill>
+          <bgColor theme="0" tint="-0.14996795556505021"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
           <bgColor theme="9" tint="0.79998168889431442"/>
         </patternFill>
       </fill>
@@ -1493,12 +2716,209 @@
       </font>
       <fill>
         <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFCDEBFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFF5F9FD"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <color rgb="FF005C00"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <color rgb="FF005C00"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <color rgb="FF005C00"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC00000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC00000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFE1E1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
           <bgColor rgb="FFFFCDCD"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF008000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF008000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF0000FF"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFF5F9FD"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFCDEBFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFCDEBFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFF5F9FD"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <color rgb="FF005C00"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC00000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFCDCD"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color auto="1"/>
       </font>
       <fill>
@@ -1509,6 +2929,92 @@
     </dxf>
     <dxf>
       <font>
+        <b val="0"/>
+        <i val="0"/>
+        <color rgb="FF005C00"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <color rgb="FF005C00"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC00000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFE1E1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFE1E1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFCDCD"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.14996795556505021"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color auto="1"/>
       </font>
       <fill>
@@ -1518,6 +3024,86 @@
       </fill>
     </dxf>
     <dxf>
+      <font>
+        <color rgb="FFC00000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC00000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <color rgb="FF005C00"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <color rgb="FF005C00"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <color rgb="FF005C00"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFF5F9FD"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
       <fill>
         <patternFill>
           <bgColor rgb="FFCDEBFF"/>
@@ -1526,13 +3112,333 @@
     </dxf>
     <dxf>
       <font>
-        <b val="0"/>
-        <i val="0"/>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFF5F9FD"/>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC00000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="3" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC00000"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF0000FF"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF0000FF"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF0000FF"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF0000FF"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF0000FF"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF0000FF"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FF006600"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FF006600"/>
+      </font>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFE5E5"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFD3E6F5"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <color rgb="FF006600"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <color rgb="FF006600"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <color rgb="FFC00000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <color rgb="FFC00000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFD9D9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFE7E7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC00000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <color rgb="FFC00000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <color rgb="FF005000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <color rgb="FF005000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC00000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC00000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFE1E1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFCDCD"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.14996795556505021"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1553,709 +3459,6 @@
         <b val="0"/>
         <i val="0"/>
         <color rgb="FF005C00"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <color rgb="FF005C00"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <color rgb="FF005C00"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC00000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC00000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFE1E1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF008000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF008000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF0000FF"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFF5F9FD"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFCDEBFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFCDEBFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFF5F9FD"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <color rgb="FF005C00"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC00000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.14996795556505021"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <color rgb="FF005C00"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC00000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFE1E1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFCDCD"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <color rgb="FF005C00"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFE1E1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFCDCD"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.14996795556505021"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC00000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC00000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <color rgb="FF005C00"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <color rgb="FF005C00"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <color rgb="FF005C00"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFF5F9FD"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFCDEBFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC00000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="3" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC00000"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF0000FF"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF0000FF"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF0000FF"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF0000FF"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF0000FF"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF0000FF"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FF006600"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FF006600"/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFE5E5"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFD3E6F5"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <color rgb="FF006600"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <color rgb="FF006600"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <color rgb="FFC00000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <color rgb="FFC00000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFD9D9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFE7E7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <color rgb="FFC00000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <color rgb="FF005000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <color rgb="FF005000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC00000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <color rgb="FF005C00"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC00000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC00000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFE1E1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFCDCD"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.14996795556505021"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <color auto="1"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2289,6 +3492,11 @@
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FFFFCDCD"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -2625,179 +3833,179 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:35" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="77" t="s">
+      <c r="A1" s="80" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="78"/>
-      <c r="C1" s="78"/>
-      <c r="D1" s="78"/>
-      <c r="E1" s="78"/>
-      <c r="F1" s="78"/>
-      <c r="G1" s="78"/>
-      <c r="H1" s="79"/>
-      <c r="I1" s="66" t="s">
+      <c r="B1" s="81"/>
+      <c r="C1" s="81"/>
+      <c r="D1" s="81"/>
+      <c r="E1" s="81"/>
+      <c r="F1" s="81"/>
+      <c r="G1" s="81"/>
+      <c r="H1" s="82"/>
+      <c r="I1" s="69" t="s">
         <v>1</v>
       </c>
-      <c r="J1" s="66"/>
-      <c r="K1" s="66"/>
-      <c r="L1" s="66"/>
-      <c r="M1" s="66"/>
-      <c r="N1" s="66"/>
-      <c r="O1" s="65"/>
-      <c r="P1" s="65"/>
-      <c r="Q1" s="65"/>
-      <c r="R1" s="65"/>
-      <c r="S1" s="65"/>
-      <c r="T1" s="65"/>
-      <c r="U1" s="65"/>
-      <c r="V1" s="65"/>
-      <c r="W1" s="65"/>
-      <c r="X1" s="65"/>
-      <c r="Y1" s="65"/>
-      <c r="Z1" s="65"/>
-      <c r="AA1" s="83" t="s">
+      <c r="J1" s="69"/>
+      <c r="K1" s="69"/>
+      <c r="L1" s="69"/>
+      <c r="M1" s="69"/>
+      <c r="N1" s="69"/>
+      <c r="O1" s="68"/>
+      <c r="P1" s="68"/>
+      <c r="Q1" s="68"/>
+      <c r="R1" s="68"/>
+      <c r="S1" s="68"/>
+      <c r="T1" s="68"/>
+      <c r="U1" s="68"/>
+      <c r="V1" s="68"/>
+      <c r="W1" s="68"/>
+      <c r="X1" s="68"/>
+      <c r="Y1" s="68"/>
+      <c r="Z1" s="68"/>
+      <c r="AA1" s="86" t="s">
         <v>2</v>
       </c>
-      <c r="AB1" s="83"/>
-      <c r="AC1" s="83"/>
-      <c r="AD1" s="83"/>
-      <c r="AE1" s="83"/>
-      <c r="AF1" s="83"/>
-      <c r="AG1" s="83"/>
-      <c r="AH1" s="83"/>
-      <c r="AI1" s="83"/>
+      <c r="AB1" s="86"/>
+      <c r="AC1" s="86"/>
+      <c r="AD1" s="86"/>
+      <c r="AE1" s="86"/>
+      <c r="AF1" s="86"/>
+      <c r="AG1" s="86"/>
+      <c r="AH1" s="86"/>
+      <c r="AI1" s="86"/>
     </row>
     <row r="2" spans="1:35" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="80"/>
-      <c r="B2" s="81"/>
-      <c r="C2" s="81"/>
-      <c r="D2" s="81"/>
-      <c r="E2" s="81"/>
-      <c r="F2" s="81"/>
-      <c r="G2" s="81"/>
-      <c r="H2" s="82"/>
-      <c r="I2" s="66" t="s">
+      <c r="A2" s="83"/>
+      <c r="B2" s="84"/>
+      <c r="C2" s="84"/>
+      <c r="D2" s="84"/>
+      <c r="E2" s="84"/>
+      <c r="F2" s="84"/>
+      <c r="G2" s="84"/>
+      <c r="H2" s="85"/>
+      <c r="I2" s="69" t="s">
         <v>3</v>
       </c>
-      <c r="J2" s="66"/>
-      <c r="K2" s="66"/>
-      <c r="L2" s="66"/>
-      <c r="M2" s="66"/>
-      <c r="N2" s="66"/>
-      <c r="O2" s="63"/>
-      <c r="P2" s="63"/>
-      <c r="Q2" s="63"/>
-      <c r="R2" s="63"/>
-      <c r="S2" s="63"/>
-      <c r="T2" s="63"/>
-      <c r="U2" s="63"/>
-      <c r="V2" s="63"/>
+      <c r="J2" s="69"/>
+      <c r="K2" s="69"/>
+      <c r="L2" s="69"/>
+      <c r="M2" s="69"/>
+      <c r="N2" s="69"/>
+      <c r="O2" s="66"/>
+      <c r="P2" s="66"/>
+      <c r="Q2" s="66"/>
+      <c r="R2" s="66"/>
+      <c r="S2" s="66"/>
+      <c r="T2" s="66"/>
+      <c r="U2" s="66"/>
+      <c r="V2" s="66"/>
       <c r="W2" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="X2" s="84"/>
-      <c r="Y2" s="85"/>
-      <c r="Z2" s="85"/>
-      <c r="AA2" s="83"/>
-      <c r="AB2" s="83"/>
-      <c r="AC2" s="83"/>
-      <c r="AD2" s="83"/>
-      <c r="AE2" s="83"/>
-      <c r="AF2" s="83"/>
-      <c r="AG2" s="83"/>
-      <c r="AH2" s="83"/>
-      <c r="AI2" s="83"/>
+      <c r="X2" s="87"/>
+      <c r="Y2" s="88"/>
+      <c r="Z2" s="88"/>
+      <c r="AA2" s="86"/>
+      <c r="AB2" s="86"/>
+      <c r="AC2" s="86"/>
+      <c r="AD2" s="86"/>
+      <c r="AE2" s="86"/>
+      <c r="AF2" s="86"/>
+      <c r="AG2" s="86"/>
+      <c r="AH2" s="86"/>
+      <c r="AI2" s="86"/>
     </row>
     <row r="3" spans="1:35" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="64" t="s">
+      <c r="A3" s="67" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="64"/>
-      <c r="C3" s="86"/>
-      <c r="D3" s="86"/>
-      <c r="E3" s="86"/>
-      <c r="F3" s="86"/>
-      <c r="G3" s="86"/>
-      <c r="H3" s="86"/>
-      <c r="I3" s="66" t="s">
+      <c r="B3" s="67"/>
+      <c r="C3" s="89"/>
+      <c r="D3" s="89"/>
+      <c r="E3" s="89"/>
+      <c r="F3" s="89"/>
+      <c r="G3" s="89"/>
+      <c r="H3" s="89"/>
+      <c r="I3" s="69" t="s">
         <v>6</v>
       </c>
-      <c r="J3" s="66"/>
-      <c r="K3" s="66"/>
-      <c r="L3" s="66"/>
-      <c r="M3" s="66"/>
-      <c r="N3" s="66"/>
-      <c r="O3" s="63"/>
-      <c r="P3" s="63"/>
-      <c r="Q3" s="63"/>
-      <c r="R3" s="63"/>
-      <c r="S3" s="63"/>
-      <c r="T3" s="63"/>
-      <c r="U3" s="63"/>
-      <c r="V3" s="63"/>
-      <c r="W3" s="63"/>
-      <c r="X3" s="63"/>
-      <c r="Y3" s="63"/>
-      <c r="Z3" s="63"/>
-      <c r="AA3" s="83"/>
-      <c r="AB3" s="83"/>
-      <c r="AC3" s="83"/>
-      <c r="AD3" s="83"/>
-      <c r="AE3" s="83"/>
-      <c r="AF3" s="83"/>
-      <c r="AG3" s="83"/>
-      <c r="AH3" s="83"/>
-      <c r="AI3" s="83"/>
+      <c r="J3" s="69"/>
+      <c r="K3" s="69"/>
+      <c r="L3" s="69"/>
+      <c r="M3" s="69"/>
+      <c r="N3" s="69"/>
+      <c r="O3" s="66"/>
+      <c r="P3" s="66"/>
+      <c r="Q3" s="66"/>
+      <c r="R3" s="66"/>
+      <c r="S3" s="66"/>
+      <c r="T3" s="66"/>
+      <c r="U3" s="66"/>
+      <c r="V3" s="66"/>
+      <c r="W3" s="66"/>
+      <c r="X3" s="66"/>
+      <c r="Y3" s="66"/>
+      <c r="Z3" s="66"/>
+      <c r="AA3" s="86"/>
+      <c r="AB3" s="86"/>
+      <c r="AC3" s="86"/>
+      <c r="AD3" s="86"/>
+      <c r="AE3" s="86"/>
+      <c r="AF3" s="86"/>
+      <c r="AG3" s="86"/>
+      <c r="AH3" s="86"/>
+      <c r="AI3" s="86"/>
     </row>
     <row r="4" spans="1:35" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="64" t="s">
+      <c r="A4" s="67" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="64"/>
-      <c r="C4" s="65"/>
-      <c r="D4" s="65"/>
-      <c r="E4" s="65"/>
-      <c r="F4" s="65"/>
-      <c r="G4" s="65"/>
-      <c r="H4" s="65"/>
-      <c r="I4" s="66" t="s">
+      <c r="B4" s="67"/>
+      <c r="C4" s="68"/>
+      <c r="D4" s="68"/>
+      <c r="E4" s="68"/>
+      <c r="F4" s="68"/>
+      <c r="G4" s="68"/>
+      <c r="H4" s="68"/>
+      <c r="I4" s="69" t="s">
         <v>8</v>
       </c>
-      <c r="J4" s="66"/>
-      <c r="K4" s="66"/>
-      <c r="L4" s="66"/>
-      <c r="M4" s="66"/>
-      <c r="N4" s="66"/>
-      <c r="O4" s="74"/>
-      <c r="P4" s="75"/>
-      <c r="Q4" s="75"/>
-      <c r="R4" s="75"/>
-      <c r="S4" s="75"/>
-      <c r="T4" s="75"/>
-      <c r="U4" s="75"/>
-      <c r="V4" s="75"/>
-      <c r="W4" s="75"/>
-      <c r="X4" s="75"/>
-      <c r="Y4" s="75"/>
-      <c r="Z4" s="76"/>
-      <c r="AA4" s="83"/>
-      <c r="AB4" s="83"/>
-      <c r="AC4" s="83"/>
-      <c r="AD4" s="83"/>
-      <c r="AE4" s="83"/>
-      <c r="AF4" s="83"/>
-      <c r="AG4" s="83"/>
-      <c r="AH4" s="83"/>
-      <c r="AI4" s="83"/>
+      <c r="J4" s="69"/>
+      <c r="K4" s="69"/>
+      <c r="L4" s="69"/>
+      <c r="M4" s="69"/>
+      <c r="N4" s="69"/>
+      <c r="O4" s="77"/>
+      <c r="P4" s="78"/>
+      <c r="Q4" s="78"/>
+      <c r="R4" s="78"/>
+      <c r="S4" s="78"/>
+      <c r="T4" s="78"/>
+      <c r="U4" s="78"/>
+      <c r="V4" s="78"/>
+      <c r="W4" s="78"/>
+      <c r="X4" s="78"/>
+      <c r="Y4" s="78"/>
+      <c r="Z4" s="79"/>
+      <c r="AA4" s="86"/>
+      <c r="AB4" s="86"/>
+      <c r="AC4" s="86"/>
+      <c r="AD4" s="86"/>
+      <c r="AE4" s="86"/>
+      <c r="AF4" s="86"/>
+      <c r="AG4" s="86"/>
+      <c r="AH4" s="86"/>
+      <c r="AI4" s="86"/>
     </row>
     <row r="5" spans="1:35" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="26" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="67" t="s">
-        <v>77</v>
-      </c>
-      <c r="C5" s="68"/>
+      <c r="B5" s="70" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5" s="71"/>
       <c r="D5" s="27">
         <v>1</v>
       </c>
@@ -2892,17 +4100,17 @@
         <v>31</v>
       </c>
       <c r="AI5" s="28" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6" spans="1:35" ht="54" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="69">
+      <c r="A6" s="72">
         <v>1</v>
       </c>
-      <c r="B6" s="72" t="s">
-        <v>11</v>
-      </c>
-      <c r="C6" s="73"/>
+      <c r="B6" s="75" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6" s="76"/>
       <c r="D6" s="3"/>
       <c r="E6" s="3"/>
       <c r="F6" s="3"/>
@@ -2936,11 +4144,11 @@
       <c r="AH6" s="23"/>
     </row>
     <row r="7" spans="1:35" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="70"/>
-      <c r="B7" s="72" t="s">
-        <v>14</v>
-      </c>
-      <c r="C7" s="73"/>
+      <c r="A7" s="73"/>
+      <c r="B7" s="75" t="s">
+        <v>13</v>
+      </c>
+      <c r="C7" s="76"/>
       <c r="D7" s="3"/>
       <c r="E7" s="3"/>
       <c r="F7" s="3"/>
@@ -2974,11 +4182,11 @@
       <c r="AH7" s="24"/>
     </row>
     <row r="8" spans="1:35" ht="57.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="71"/>
-      <c r="B8" s="72" t="s">
-        <v>73</v>
-      </c>
-      <c r="C8" s="73"/>
+      <c r="A8" s="74"/>
+      <c r="B8" s="75" t="s">
+        <v>14</v>
+      </c>
+      <c r="C8" s="76"/>
       <c r="D8" s="3"/>
       <c r="E8" s="3"/>
       <c r="F8" s="3"/>
@@ -3019,10 +4227,10 @@
       <c r="A9" s="18">
         <v>2</v>
       </c>
-      <c r="B9" s="45" t="s">
+      <c r="B9" s="48" t="s">
         <v>15</v>
       </c>
-      <c r="C9" s="46"/>
+      <c r="C9" s="49"/>
       <c r="D9" s="3"/>
       <c r="E9" s="3"/>
       <c r="F9" s="3"/>
@@ -3063,10 +4271,10 @@
       <c r="A10" s="32">
         <v>3</v>
       </c>
-      <c r="B10" s="54" t="s">
-        <v>74</v>
-      </c>
-      <c r="C10" s="55"/>
+      <c r="B10" s="57" t="s">
+        <v>16</v>
+      </c>
+      <c r="C10" s="58"/>
       <c r="D10" s="3"/>
       <c r="E10" s="3"/>
       <c r="F10" s="3"/>
@@ -3107,10 +4315,10 @@
       <c r="A11" s="18">
         <v>4</v>
       </c>
-      <c r="B11" s="56" t="s">
-        <v>16</v>
-      </c>
-      <c r="C11" s="46"/>
+      <c r="B11" s="59" t="s">
+        <v>17</v>
+      </c>
+      <c r="C11" s="49"/>
       <c r="D11" s="3"/>
       <c r="E11" s="3"/>
       <c r="F11" s="3"/>
@@ -3144,14 +4352,14 @@
       <c r="AH11" s="25"/>
     </row>
     <row r="12" spans="1:35" ht="51.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="41">
+      <c r="A12" s="44">
         <v>5</v>
       </c>
-      <c r="B12" s="43" t="s">
-        <v>17</v>
+      <c r="B12" s="46" t="s">
+        <v>18</v>
       </c>
       <c r="C12" s="22" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D12" s="3"/>
       <c r="E12" s="3"/>
@@ -3186,10 +4394,10 @@
       <c r="AH12" s="24"/>
     </row>
     <row r="13" spans="1:35" ht="45.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="57"/>
-      <c r="B13" s="58"/>
+      <c r="A13" s="60"/>
+      <c r="B13" s="61"/>
       <c r="C13" s="21" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D13" s="3"/>
       <c r="E13" s="3"/>
@@ -3224,10 +4432,10 @@
       <c r="AH13" s="24"/>
     </row>
     <row r="14" spans="1:35" ht="41.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="57"/>
-      <c r="B14" s="58"/>
+      <c r="A14" s="60"/>
+      <c r="B14" s="61"/>
       <c r="C14" s="21" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D14" s="3"/>
       <c r="E14" s="3"/>
@@ -3266,10 +4474,10 @@
       </c>
     </row>
     <row r="15" spans="1:35" ht="56.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="42"/>
-      <c r="B15" s="44"/>
+      <c r="A15" s="45"/>
+      <c r="B15" s="47"/>
       <c r="C15" s="21" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D15" s="3"/>
       <c r="E15" s="3"/>
@@ -3304,14 +4512,14 @@
       <c r="AH15" s="25"/>
     </row>
     <row r="16" spans="1:35" ht="54" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="59">
+      <c r="A16" s="62">
         <v>6</v>
       </c>
-      <c r="B16" s="61" t="s">
-        <v>22</v>
+      <c r="B16" s="64" t="s">
+        <v>23</v>
       </c>
       <c r="C16" s="19" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
@@ -3346,10 +4554,10 @@
       <c r="AH16" s="25"/>
     </row>
     <row r="17" spans="1:35" ht="51.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="60"/>
-      <c r="B17" s="62"/>
+      <c r="A17" s="63"/>
+      <c r="B17" s="65"/>
       <c r="C17" s="20" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D17" s="3"/>
       <c r="E17" s="3"/>
@@ -3388,14 +4596,14 @@
       </c>
     </row>
     <row r="18" spans="1:35" ht="42" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="41">
+      <c r="A18" s="44">
         <v>7</v>
       </c>
-      <c r="B18" s="43" t="s">
-        <v>25</v>
+      <c r="B18" s="46" t="s">
+        <v>26</v>
       </c>
       <c r="C18" s="21" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D18" s="3"/>
       <c r="E18" s="3"/>
@@ -3430,10 +4638,10 @@
       <c r="AH18" s="25"/>
     </row>
     <row r="19" spans="1:35" ht="51" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="42"/>
-      <c r="B19" s="44"/>
+      <c r="A19" s="45"/>
+      <c r="B19" s="47"/>
       <c r="C19" s="21" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D19" s="3"/>
       <c r="E19" s="3"/>
@@ -3475,10 +4683,10 @@
       <c r="A20" s="18">
         <v>8</v>
       </c>
-      <c r="B20" s="45" t="s">
-        <v>26</v>
-      </c>
-      <c r="C20" s="46"/>
+      <c r="B20" s="48" t="s">
+        <v>27</v>
+      </c>
+      <c r="C20" s="49"/>
       <c r="D20" s="3"/>
       <c r="E20" s="3"/>
       <c r="F20" s="3"/>
@@ -3556,40 +4764,40 @@
       <c r="A22" s="7"/>
       <c r="B22" s="8"/>
       <c r="C22" s="10" t="s">
-        <v>27</v>
-      </c>
-      <c r="D22" s="47"/>
-      <c r="E22" s="48"/>
-      <c r="F22" s="48"/>
-      <c r="G22" s="48"/>
-      <c r="H22" s="48"/>
-      <c r="I22" s="48"/>
-      <c r="J22" s="48"/>
-      <c r="K22" s="48"/>
-      <c r="L22" s="48"/>
-      <c r="M22" s="48"/>
-      <c r="N22" s="48"/>
-      <c r="O22" s="48"/>
-      <c r="P22" s="48"/>
-      <c r="Q22" s="48"/>
-      <c r="R22" s="48"/>
-      <c r="S22" s="48"/>
-      <c r="T22" s="48"/>
-      <c r="U22" s="48"/>
-      <c r="V22" s="48"/>
-      <c r="W22" s="48"/>
-      <c r="X22" s="48"/>
-      <c r="Y22" s="48"/>
-      <c r="Z22" s="48"/>
-      <c r="AA22" s="48"/>
-      <c r="AB22" s="48"/>
-      <c r="AC22" s="48"/>
-      <c r="AD22" s="48"/>
-      <c r="AE22" s="48"/>
-      <c r="AF22" s="48"/>
-      <c r="AG22" s="48"/>
-      <c r="AH22" s="48"/>
-      <c r="AI22" s="49"/>
+        <v>28</v>
+      </c>
+      <c r="D22" s="50"/>
+      <c r="E22" s="51"/>
+      <c r="F22" s="51"/>
+      <c r="G22" s="51"/>
+      <c r="H22" s="51"/>
+      <c r="I22" s="51"/>
+      <c r="J22" s="51"/>
+      <c r="K22" s="51"/>
+      <c r="L22" s="51"/>
+      <c r="M22" s="51"/>
+      <c r="N22" s="51"/>
+      <c r="O22" s="51"/>
+      <c r="P22" s="51"/>
+      <c r="Q22" s="51"/>
+      <c r="R22" s="51"/>
+      <c r="S22" s="51"/>
+      <c r="T22" s="51"/>
+      <c r="U22" s="51"/>
+      <c r="V22" s="51"/>
+      <c r="W22" s="51"/>
+      <c r="X22" s="51"/>
+      <c r="Y22" s="51"/>
+      <c r="Z22" s="51"/>
+      <c r="AA22" s="51"/>
+      <c r="AB22" s="51"/>
+      <c r="AC22" s="51"/>
+      <c r="AD22" s="51"/>
+      <c r="AE22" s="51"/>
+      <c r="AF22" s="51"/>
+      <c r="AG22" s="51"/>
+      <c r="AH22" s="51"/>
+      <c r="AI22" s="52"/>
     </row>
     <row r="23" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A23" s="9"/>
@@ -3632,36 +4840,36 @@
       <c r="A24" s="9"/>
       <c r="B24" s="11"/>
       <c r="C24" s="10" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D24" s="30" t="s">
-        <v>13</v>
-      </c>
-      <c r="E24" s="50" t="s">
-        <v>29</v>
-      </c>
-      <c r="F24" s="50"/>
-      <c r="G24" s="51"/>
+        <v>30</v>
+      </c>
+      <c r="E24" s="53" t="s">
+        <v>31</v>
+      </c>
+      <c r="F24" s="53"/>
+      <c r="G24" s="54"/>
       <c r="H24" s="30" t="s">
-        <v>12</v>
-      </c>
-      <c r="I24" s="52" t="s">
-        <v>30</v>
-      </c>
-      <c r="J24" s="52"/>
-      <c r="K24" s="52"/>
-      <c r="L24" s="52"/>
-      <c r="M24" s="52"/>
-      <c r="N24" s="52"/>
-      <c r="O24" s="53"/>
+        <v>32</v>
+      </c>
+      <c r="I24" s="55" t="s">
+        <v>33</v>
+      </c>
+      <c r="J24" s="55"/>
+      <c r="K24" s="55"/>
+      <c r="L24" s="55"/>
+      <c r="M24" s="55"/>
+      <c r="N24" s="55"/>
+      <c r="O24" s="56"/>
       <c r="P24" s="30" t="s">
-        <v>31</v>
-      </c>
-      <c r="Q24" s="50" t="s">
-        <v>32</v>
-      </c>
-      <c r="R24" s="50"/>
-      <c r="S24" s="51"/>
+        <v>34</v>
+      </c>
+      <c r="Q24" s="53" t="s">
+        <v>35</v>
+      </c>
+      <c r="R24" s="53"/>
+      <c r="S24" s="54"/>
       <c r="T24" s="9"/>
       <c r="U24" s="9"/>
       <c r="V24" s="9"/>
@@ -3681,196 +4889,196 @@
     </row>
     <row r="25" spans="1:35" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="9"/>
-      <c r="B25" s="87" t="s">
-        <v>78</v>
+      <c r="B25" s="33" t="s">
+        <v>36</v>
       </c>
       <c r="C25" s="11"/>
       <c r="D25" s="30" t="s">
-        <v>75</v>
-      </c>
-      <c r="E25" s="33" t="s">
-        <v>33</v>
-      </c>
-      <c r="F25" s="33"/>
-      <c r="G25" s="36"/>
+        <v>37</v>
+      </c>
+      <c r="E25" s="36" t="s">
+        <v>38</v>
+      </c>
+      <c r="F25" s="36"/>
+      <c r="G25" s="39"/>
       <c r="H25" s="31" t="s">
-        <v>34</v>
-      </c>
-      <c r="I25" s="37" t="s">
-        <v>35</v>
-      </c>
-      <c r="J25" s="37"/>
-      <c r="K25" s="38"/>
+        <v>39</v>
+      </c>
+      <c r="I25" s="40" t="s">
+        <v>40</v>
+      </c>
+      <c r="J25" s="40"/>
+      <c r="K25" s="41"/>
       <c r="L25" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="M25" s="34" t="s">
-        <v>37</v>
-      </c>
-      <c r="N25" s="34"/>
-      <c r="O25" s="35"/>
+        <v>41</v>
+      </c>
+      <c r="M25" s="37" t="s">
+        <v>42</v>
+      </c>
+      <c r="N25" s="37"/>
+      <c r="O25" s="38"/>
       <c r="P25" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q25" s="34" t="s">
-        <v>39</v>
-      </c>
-      <c r="R25" s="34"/>
-      <c r="S25" s="35"/>
+        <v>43</v>
+      </c>
+      <c r="Q25" s="37" t="s">
+        <v>44</v>
+      </c>
+      <c r="R25" s="37"/>
+      <c r="S25" s="38"/>
       <c r="T25" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="U25" s="34" t="s">
-        <v>41</v>
-      </c>
-      <c r="V25" s="34"/>
-      <c r="W25" s="35"/>
+        <v>45</v>
+      </c>
+      <c r="U25" s="37" t="s">
+        <v>46</v>
+      </c>
+      <c r="V25" s="37"/>
+      <c r="W25" s="38"/>
       <c r="X25" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="Y25" s="34" t="s">
-        <v>43</v>
-      </c>
-      <c r="Z25" s="34"/>
-      <c r="AA25" s="35"/>
+        <v>47</v>
+      </c>
+      <c r="Y25" s="37" t="s">
+        <v>48</v>
+      </c>
+      <c r="Z25" s="37"/>
+      <c r="AA25" s="38"/>
       <c r="AB25" s="15" t="s">
-        <v>44</v>
-      </c>
-      <c r="AC25" s="34" t="s">
-        <v>45</v>
-      </c>
-      <c r="AD25" s="34"/>
-      <c r="AE25" s="35"/>
+        <v>49</v>
+      </c>
+      <c r="AC25" s="37" t="s">
+        <v>50</v>
+      </c>
+      <c r="AD25" s="37"/>
+      <c r="AE25" s="38"/>
       <c r="AF25" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="AG25" s="34" t="s">
-        <v>47</v>
-      </c>
-      <c r="AH25" s="34"/>
-      <c r="AI25" s="35"/>
+        <v>51</v>
+      </c>
+      <c r="AG25" s="37" t="s">
+        <v>52</v>
+      </c>
+      <c r="AH25" s="37"/>
+      <c r="AI25" s="38"/>
     </row>
     <row r="26" spans="1:35" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="9"/>
-      <c r="B26" s="88" t="s">
-        <v>79</v>
+      <c r="B26" s="34" t="s">
+        <v>53</v>
       </c>
       <c r="C26" s="11"/>
       <c r="D26" s="16" t="s">
-        <v>76</v>
-      </c>
-      <c r="E26" s="34" t="s">
-        <v>48</v>
-      </c>
-      <c r="F26" s="34"/>
-      <c r="G26" s="35"/>
+        <v>54</v>
+      </c>
+      <c r="E26" s="37" t="s">
+        <v>55</v>
+      </c>
+      <c r="F26" s="37"/>
+      <c r="G26" s="38"/>
       <c r="H26" s="16" t="s">
-        <v>49</v>
-      </c>
-      <c r="I26" s="39" t="s">
-        <v>50</v>
-      </c>
-      <c r="J26" s="39"/>
-      <c r="K26" s="40"/>
+        <v>56</v>
+      </c>
+      <c r="I26" s="42" t="s">
+        <v>57</v>
+      </c>
+      <c r="J26" s="42"/>
+      <c r="K26" s="43"/>
       <c r="L26" s="16" t="s">
-        <v>51</v>
-      </c>
-      <c r="M26" s="34" t="s">
-        <v>52</v>
-      </c>
-      <c r="N26" s="34"/>
-      <c r="O26" s="35"/>
+        <v>58</v>
+      </c>
+      <c r="M26" s="37" t="s">
+        <v>59</v>
+      </c>
+      <c r="N26" s="37"/>
+      <c r="O26" s="38"/>
       <c r="P26" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="Q26" s="34" t="s">
-        <v>54</v>
-      </c>
-      <c r="R26" s="34"/>
-      <c r="S26" s="35"/>
+        <v>60</v>
+      </c>
+      <c r="Q26" s="37" t="s">
+        <v>61</v>
+      </c>
+      <c r="R26" s="37"/>
+      <c r="S26" s="38"/>
       <c r="T26" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="U26" s="34" t="s">
-        <v>56</v>
-      </c>
-      <c r="V26" s="34"/>
-      <c r="W26" s="35"/>
+        <v>62</v>
+      </c>
+      <c r="U26" s="37" t="s">
+        <v>63</v>
+      </c>
+      <c r="V26" s="37"/>
+      <c r="W26" s="38"/>
       <c r="X26" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="Y26" s="34" t="s">
-        <v>58</v>
-      </c>
-      <c r="Z26" s="34"/>
-      <c r="AA26" s="35"/>
+        <v>64</v>
+      </c>
+      <c r="Y26" s="37" t="s">
+        <v>65</v>
+      </c>
+      <c r="Z26" s="37"/>
+      <c r="AA26" s="38"/>
       <c r="AB26" s="17" t="s">
-        <v>59</v>
-      </c>
-      <c r="AC26" s="33" t="s">
-        <v>60</v>
-      </c>
-      <c r="AD26" s="33"/>
-      <c r="AE26" s="36"/>
+        <v>66</v>
+      </c>
+      <c r="AC26" s="36" t="s">
+        <v>67</v>
+      </c>
+      <c r="AD26" s="36"/>
+      <c r="AE26" s="39"/>
       <c r="AF26" s="15" t="s">
-        <v>61</v>
-      </c>
-      <c r="AG26" s="33" t="s">
-        <v>62</v>
-      </c>
-      <c r="AH26" s="33"/>
-      <c r="AI26" s="36"/>
+        <v>68</v>
+      </c>
+      <c r="AG26" s="36" t="s">
+        <v>69</v>
+      </c>
+      <c r="AH26" s="36"/>
+      <c r="AI26" s="39"/>
     </row>
     <row r="27" spans="1:35" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="9"/>
-      <c r="B27" s="89" t="s">
-        <v>80</v>
+      <c r="B27" s="35" t="s">
+        <v>70</v>
       </c>
       <c r="C27" s="11"/>
       <c r="D27" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="E27" s="33" t="s">
-        <v>64</v>
-      </c>
-      <c r="F27" s="33"/>
-      <c r="G27" s="33"/>
+        <v>71</v>
+      </c>
+      <c r="E27" s="36" t="s">
+        <v>72</v>
+      </c>
+      <c r="F27" s="36"/>
+      <c r="G27" s="36"/>
       <c r="H27" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="I27" s="34" t="s">
-        <v>66</v>
-      </c>
-      <c r="J27" s="34"/>
-      <c r="K27" s="34"/>
-      <c r="L27" s="34"/>
-      <c r="M27" s="34"/>
-      <c r="N27" s="34"/>
-      <c r="O27" s="35"/>
+        <v>73</v>
+      </c>
+      <c r="I27" s="37" t="s">
+        <v>74</v>
+      </c>
+      <c r="J27" s="37"/>
+      <c r="K27" s="37"/>
+      <c r="L27" s="37"/>
+      <c r="M27" s="37"/>
+      <c r="N27" s="37"/>
+      <c r="O27" s="38"/>
       <c r="P27" s="16" t="s">
-        <v>67</v>
-      </c>
-      <c r="Q27" s="33" t="s">
-        <v>68</v>
-      </c>
-      <c r="R27" s="33"/>
-      <c r="S27" s="36"/>
+        <v>75</v>
+      </c>
+      <c r="Q27" s="36" t="s">
+        <v>76</v>
+      </c>
+      <c r="R27" s="36"/>
+      <c r="S27" s="39"/>
       <c r="T27" s="16" t="s">
-        <v>69</v>
-      </c>
-      <c r="U27" s="33" t="s">
-        <v>70</v>
-      </c>
-      <c r="V27" s="33"/>
-      <c r="W27" s="36"/>
+        <v>77</v>
+      </c>
+      <c r="U27" s="36" t="s">
+        <v>78</v>
+      </c>
+      <c r="V27" s="36"/>
+      <c r="W27" s="39"/>
       <c r="X27" s="16" t="s">
-        <v>71</v>
-      </c>
-      <c r="Y27" s="33" t="s">
-        <v>72</v>
-      </c>
-      <c r="Z27" s="33"/>
-      <c r="AA27" s="36"/>
+        <v>79</v>
+      </c>
+      <c r="Y27" s="36" t="s">
+        <v>80</v>
+      </c>
+      <c r="Z27" s="36"/>
+      <c r="AA27" s="39"/>
       <c r="AB27" s="9"/>
       <c r="AC27" s="9"/>
       <c r="AD27" s="9"/>
@@ -3938,452 +5146,14 @@
     <mergeCell ref="U27:W27"/>
     <mergeCell ref="Y27:AA27"/>
   </mergeCells>
-  <conditionalFormatting sqref="A1 I1:I4 O1:O4 A3:A4 C3:C4 D23:M23 X25:Y25 D26:D27 T26:Y27">
-    <cfRule type="cellIs" dxfId="133" priority="114" operator="equal">
-      <formula>"ZWO"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="132" priority="113" operator="equal">
-      <formula>"ŚWREH"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="131" priority="112" operator="equal">
-      <formula>"ŚWREH"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="130" priority="120" operator="equal">
-      <formula>"WD"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="129" priority="119" operator="equal">
-      <formula>"WN"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="128" priority="118" operator="equal">
-      <formula>"WN"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="127" priority="117" operator="equal">
-      <formula>"UW"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="126" priority="116" operator="equal">
-      <formula>"UWŻ"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="125" priority="115" operator="equal">
-      <formula>"ZWL"</formula>
+  <conditionalFormatting sqref="D6:AH6">
+    <cfRule type="expression" dxfId="2" priority="1">
+      <formula>AND((24-C7+D6)&lt;11,C7&lt;&gt;"",D6&lt;&gt;"")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A1 I1:I4 O1:O4 A3:A4 C3:C4 D23:M23 X25:Y25 T26:Y27">
-    <cfRule type="cellIs" dxfId="124" priority="121" operator="equal">
-      <formula>"WŚ"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A1 I1:I4 O1:O4 W2:X2 A3:A4 C3:C4">
-    <cfRule type="cellIs" dxfId="123" priority="106" operator="equal">
-      <formula>"UW"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="122" priority="107" operator="equal">
-      <formula>"ZWO"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="121" priority="108" operator="equal">
-      <formula>"ZWL"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="120" priority="109" operator="equal">
-      <formula>"WŚ"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="119" priority="110" operator="equal">
-      <formula>"WD"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="118" priority="105" operator="equal">
-      <formula>"UWŻ"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="117" priority="111" operator="equal">
-      <formula>"WN"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A1:AI3 A4:O4 AA4:AI4 A5:AI5 A6:AH7 A8:AI10 A11:AH13 A14:AI14 A15:AH16 A17:AI17 A18:AH18 A19:AI23 A24:C24 T24:AI27 C26:D27 A25:A27 C25">
-    <cfRule type="cellIs" dxfId="116" priority="2" operator="equal">
-      <formula>"WN"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="115" priority="3" operator="equal">
-      <formula>"WD"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="114" priority="4" operator="equal">
-      <formula>"UWŻ"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="113" priority="5" operator="equal">
-      <formula>"UW"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="112" priority="6" operator="equal">
-      <formula>"ZWO"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="111" priority="7" operator="equal">
-      <formula>"ZWL"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="110" priority="8" operator="equal">
-      <formula>"WŚ"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="109" priority="9" operator="equal">
-      <formula>"WD"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="108" priority="10" operator="equal">
-      <formula>"WD"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="107" priority="11" operator="equal">
-      <formula>"WD"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="106" priority="12" operator="equal">
-      <formula>"WN"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B6:B10">
-    <cfRule type="cellIs" dxfId="105" priority="100" operator="equal">
-      <formula>"OP"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="104" priority="101" operator="equal">
-      <formula>"CH"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B10">
-    <cfRule type="cellIs" priority="90" operator="equal">
-      <formula>"WP"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="103" priority="89" operator="equal">
-      <formula>"D"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="102" priority="88" operator="equal">
-      <formula>"NP"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="101" priority="87" operator="equal">
-      <formula>"NB"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="100" priority="86" operator="equal">
-      <formula>"NN"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="99" priority="85" operator="equal">
-      <formula>"DEL"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="98" priority="84" operator="equal">
-      <formula>"ZW"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="97" priority="83" operator="equal">
-      <formula>"WN"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="96" priority="102" operator="equal">
-      <formula>"W5"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="95" priority="104" operator="equal">
-      <formula>"WN"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="94" priority="103" operator="equal">
-      <formula>"WŚ"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="93" priority="99" operator="equal">
-      <formula>"UW"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="92" priority="97" operator="equal">
-      <formula>"UO"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="91" priority="98" operator="equal">
-      <formula>"UW"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="96" operator="equal">
-      <formula>"UO"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="90" priority="95" operator="equal">
-      <formula>"UOP"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="89" priority="94" operator="equal">
-      <formula>"UM"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="88" priority="93" operator="equal">
-      <formula>"UR"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="87" priority="92" operator="equal">
-      <formula>"Uwych"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="86" priority="91" operator="equal">
-      <formula>"UB"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C22">
-    <cfRule type="cellIs" dxfId="85" priority="13" operator="equal">
-      <formula>"WD"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="84" priority="14" operator="equal">
-      <formula>"WD"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="83" priority="15" operator="equal">
-      <formula>"ŚWREH"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="82" priority="16" operator="equal">
-      <formula>"ŚWREH"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="81" priority="17" operator="equal">
-      <formula>"ZWO"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="80" priority="18" operator="equal">
-      <formula>"ZWL"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="79" priority="19" operator="equal">
-      <formula>"UWŻ"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="78" priority="20" operator="equal">
-      <formula>"UW"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="77" priority="24" operator="equal">
-      <formula>"WŚ"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="76" priority="23" operator="equal">
-      <formula>"WD"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="75" priority="22" operator="equal">
-      <formula>"WN"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="74" priority="21" operator="equal">
-      <formula>"WN"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C24">
-    <cfRule type="cellIs" dxfId="73" priority="28" operator="equal">
-      <formula>"ŚWREH"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="72" priority="34" operator="equal">
-      <formula>"WN"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="71" priority="33" operator="equal">
-      <formula>"WN"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="70" priority="32" operator="equal">
-      <formula>"UW"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="69" priority="30" operator="equal">
-      <formula>"ZWL"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="68" priority="36" operator="equal">
-      <formula>"WŚ"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="67" priority="35" operator="equal">
-      <formula>"WD"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="66" priority="31" operator="equal">
-      <formula>"UWŻ"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="65" priority="29" operator="equal">
-      <formula>"ZWO"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="64" priority="27" operator="equal">
-      <formula>"ŚWREH"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="63" priority="26" operator="equal">
-      <formula>"WD"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="62" priority="25" operator="equal">
-      <formula>"WD"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D23:M23 X25:Y25 AF25:AG26 D26:D27 T26:Y27">
-    <cfRule type="cellIs" dxfId="61" priority="61" operator="equal">
-      <formula>"WD"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="60" priority="62" operator="equal">
-      <formula>"WD"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E16:G16 J16:AH16">
-    <cfRule type="cellIs" dxfId="59" priority="146" operator="equal">
-      <formula>"WP"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E18:G18 J18:AH18">
-    <cfRule type="cellIs" dxfId="58" priority="149" operator="equal">
-      <formula>"UW"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="57" priority="147" operator="equal">
-      <formula>"OP"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="56" priority="148" operator="equal">
-      <formula>"CH"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="T25:U25">
-    <cfRule type="cellIs" dxfId="55" priority="45" operator="equal">
-      <formula>"WN"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="54" priority="44" operator="equal">
-      <formula>"UW"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="53" priority="43" operator="equal">
-      <formula>"UWŻ"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="52" priority="42" operator="equal">
-      <formula>"ZWL"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="51" priority="41" operator="equal">
-      <formula>"ZWO"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="50" priority="40" operator="equal">
-      <formula>"ŚWREH"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="49" priority="39" operator="equal">
-      <formula>"ŚWREH"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="48" priority="38" operator="equal">
-      <formula>"WD"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="47" priority="37" operator="equal">
-      <formula>"WD"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="46" priority="48" operator="equal">
-      <formula>"WŚ"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="45" priority="47" operator="equal">
-      <formula>"WD"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="44" priority="46" operator="equal">
-      <formula>"WN"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="W2">
-    <cfRule type="cellIs" dxfId="43" priority="122" operator="equal">
-      <formula>"WD"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="42" priority="123" operator="equal">
-      <formula>"WŚ"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AA1 A5:AI5 A6:B6 D6:AH7 B7:B8 D8:AI10 A9:B9 A11:C12 D11:AH13 A13:A15 C13:C15 D14:AI14 D15:AH16 A16:C16 A17 C17:AI17 A18:AH18 A19 C19 D19:AI20 A20:B20 A21:AI21 A22:B22 D22 A23:C23 N23:AI23 A24:B24 T24:AI24 A25:A27 AB27:AH27 C25:C27">
-    <cfRule type="cellIs" dxfId="41" priority="129" operator="equal">
-      <formula>"NP"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="40" priority="130" operator="equal">
-      <formula>"D"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="131" operator="equal">
-      <formula>"WP"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="39" priority="133" operator="equal">
-      <formula>"Uwych"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="38" priority="134" operator="equal">
-      <formula>"UR"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="37" priority="135" operator="equal">
-      <formula>"UM"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="36" priority="128" operator="equal">
-      <formula>"NB"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="35" priority="136" operator="equal">
-      <formula>"UOP"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="137" operator="equal">
-      <formula>"UO"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="34" priority="138" operator="equal">
-      <formula>"UO"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="33" priority="139" operator="equal">
-      <formula>"UW"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="32" priority="140" operator="equal">
-      <formula>"UW"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="31" priority="143" operator="equal">
-      <formula>"W5"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="30" priority="144" operator="equal">
-      <formula>"WŚ"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="29" priority="145" operator="equal">
-      <formula>"WN"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="28" priority="132" operator="equal">
-      <formula>"UB"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="27" priority="124" operator="equal">
-      <formula>"WN"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="26" priority="125" operator="equal">
-      <formula>"ZW"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="25" priority="126" operator="equal">
-      <formula>"DEL"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="24" priority="127" operator="equal">
-      <formula>"NN"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AA1 B5:AI5 D6:AH7 D8:AI10 B11:C12 D11:AH13 C13:C15 D14:AI14 D15:AH16 B16:C16 C17:AI17 B18:AH18 C19 D19:AI20 B20 B21:AI21 B22 D22 B23:C23 N23:AI23 B24 T24:AI24 C25:C27 AB27:AH27">
-    <cfRule type="cellIs" dxfId="23" priority="141" operator="equal">
-      <formula>"OP"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="22" priority="142" operator="equal">
-      <formula>"CH"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AB25:AC26">
-    <cfRule type="cellIs" dxfId="21" priority="58" operator="equal">
-      <formula>"WN"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="20" priority="57" operator="equal">
-      <formula>"WN"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="19" priority="56" operator="equal">
-      <formula>"UW"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="18" priority="55" operator="equal">
-      <formula>"UWŻ"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="17" priority="53" operator="equal">
-      <formula>"ZWO"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="16" priority="51" operator="equal">
-      <formula>"ŚWREH"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="15" priority="50" operator="equal">
-      <formula>"WD"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="14" priority="49" operator="equal">
-      <formula>"WD"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="13" priority="52" operator="equal">
-      <formula>"ŚWREH"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="12" priority="54" operator="equal">
-      <formula>"ZWL"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="11" priority="59" operator="equal">
-      <formula>"WD"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="10" priority="60" operator="equal">
-      <formula>"WŚ"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AF25:AG26">
-    <cfRule type="cellIs" dxfId="9" priority="71" operator="equal">
-      <formula>"WD"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="8" priority="72" operator="equal">
-      <formula>"WŚ"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="7" priority="70" operator="equal">
-      <formula>"WN"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="6" priority="69" operator="equal">
-      <formula>"WN"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="5" priority="68" operator="equal">
-      <formula>"UW"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="4" priority="66" operator="equal">
-      <formula>"ZWL"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="3" priority="67" operator="equal">
-      <formula>"UWŻ"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="65" operator="equal">
-      <formula>"ZWO"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="64" operator="equal">
-      <formula>"ŚWREH"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="63" operator="equal">
-      <formula>"ŚWREH"</formula>
+  <conditionalFormatting sqref="C7:AG7">
+    <cfRule type="expression" dxfId="1" priority="2">
+      <formula>AND((24-C7+D6)&lt;11,D6&lt;&gt;"",C7&lt;&gt;"")</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
